--- a/AULA 02-PTIC.xlsx
+++ b/AULA 02-PTIC.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CAMARGO\Desktop\PTIC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A2B2C29-221B-4C4A-9F53-8F7E636EE2C4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9410C72-B999-4112-AE51-9F606A002F56}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{28501F88-7677-4DF6-9970-B00A37CC8A76}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{28501F88-7677-4DF6-9970-B00A37CC8A76}"/>
   </bookViews>
   <sheets>
     <sheet name="Notas" sheetId="1" r:id="rId1"/>
+    <sheet name="Comissão de Vendas " sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="BOLETIM">Notas!$A$1:$H$7</definedName>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>Planilha de notas</t>
   </si>
@@ -76,13 +77,61 @@
   </si>
   <si>
     <t>Situação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comissão de vendas </t>
+  </si>
+  <si>
+    <t>Nome do Vendedor</t>
+  </si>
+  <si>
+    <t>Departamento</t>
+  </si>
+  <si>
+    <t>Valor da Venda</t>
+  </si>
+  <si>
+    <t>Limite mínimo</t>
+  </si>
+  <si>
+    <t>Porcentagem da Comissão</t>
+  </si>
+  <si>
+    <t>Maria Eduarda</t>
+  </si>
+  <si>
+    <t>Luiz Henrique</t>
+  </si>
+  <si>
+    <t>Sabrina da Silva</t>
+  </si>
+  <si>
+    <t>Valor da Comissão</t>
+  </si>
+  <si>
+    <t>Lorenna Alves</t>
+  </si>
+  <si>
+    <t>Skin care</t>
+  </si>
+  <si>
+    <t>Maquiagem</t>
+  </si>
+  <si>
+    <t>Unha</t>
+  </si>
+  <si>
+    <t>Valor de Comissão alta</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -118,8 +167,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -155,8 +227,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -179,12 +281,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -204,38 +317,32 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="5" fillId="7" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
+    <cellStyle name="20% - Ênfase2" xfId="2" builtinId="34"/>
+    <cellStyle name="60% - Ênfase2" xfId="3" builtinId="36"/>
     <cellStyle name="Ênfase5" xfId="1" builtinId="45"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="91">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="13">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -363,766 +470,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1298,6 +645,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-423D-4069-B298-32C490F637EC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1341,6 +693,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-423D-4069-B298-32C490F637EC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1384,6 +741,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-423D-4069-B298-32C490F637EC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -1430,6 +792,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-423D-4069-B298-32C490F637EC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -1476,6 +843,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-423D-4069-B298-32C490F637EC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -2599,16 +1971,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="8">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="7">
         <f ca="1">TODAY()</f>
         <v>46286</v>
       </c>
@@ -2807,42 +2179,42 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="G3:G7">
-    <cfRule type="cellIs" dxfId="24" priority="4" operator="between">
+    <cfRule type="cellIs" dxfId="12" priority="4" operator="between">
       <formula>5</formula>
       <formula>6.99</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="lessThan">
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="6" operator="greaterThan">
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="7" operator="between">
+    <cfRule type="cellIs" dxfId="9" priority="7" operator="between">
       <formula>5</formula>
       <formula>6.99</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="8" operator="between">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="between">
       <formula>5</formula>
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="9" operator="lessThan">
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="10" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="aboveAverage" dxfId="17" priority="11" equalAverage="1"/>
-    <cfRule type="aboveAverage" dxfId="16" priority="12" aboveAverage="0"/>
-    <cfRule type="aboveAverage" dxfId="15" priority="13"/>
+    <cfRule type="aboveAverage" dxfId="5" priority="11" equalAverage="1"/>
+    <cfRule type="aboveAverage" dxfId="4" priority="12" aboveAverage="0"/>
+    <cfRule type="aboveAverage" dxfId="3" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H7">
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="APROVADO">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="APROVADO">
       <formula>NOT(ISERROR(SEARCH("APROVADO",H3)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="RECUPERAÇÃO">
       <formula>NOT(ISERROR(SEARCH("RECUPERAÇÃO",H3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="REPROVADO">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="REPROVADO">
       <formula>NOT(ISERROR(SEARCH("REPROVADO",H3)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2850,4 +2222,175 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7194E76-DEDA-4B2E-94B4-90155E6067DA}">
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="11">
+        <v>12000</v>
+      </c>
+      <c r="D4" s="11">
+        <v>7000</v>
+      </c>
+      <c r="E4" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="F4" s="10">
+        <f>IF(C4&lt;D4,0,C4*E4)</f>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="11">
+        <v>14000</v>
+      </c>
+      <c r="D5" s="11">
+        <v>8000</v>
+      </c>
+      <c r="E5" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="F5" s="10">
+        <f t="shared" ref="F5:F7" si="0">IF(C5&lt;D5,0,C5*E5)</f>
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="11">
+        <v>8000</v>
+      </c>
+      <c r="D6" s="11">
+        <v>5000</v>
+      </c>
+      <c r="E6" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="F6" s="10">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="11">
+        <v>9000</v>
+      </c>
+      <c r="D7" s="11">
+        <v>7000</v>
+      </c>
+      <c r="E7" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="F7" s="10">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="15"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="14">
+        <v>1</v>
+      </c>
+      <c r="B11" s="14">
+        <f>LARGE(F4:F7,1)</f>
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="14">
+        <v>2</v>
+      </c>
+      <c r="B12" s="14">
+        <f>LARGE(F4:F7,2)</f>
+        <v>1200</v>
+      </c>
+      <c r="C12" s="16"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="14">
+        <v>3</v>
+      </c>
+      <c r="B13" s="14">
+        <f>LARGE(F4:F7,3)</f>
+        <v>900</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A10:B10"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/AULA 02-PTIC.xlsx
+++ b/AULA 02-PTIC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CAMARGO\Desktop\PTIC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9410C72-B999-4112-AE51-9F606A002F56}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1418F2E-291D-4462-96C0-17705FFB1462}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{28501F88-7677-4DF6-9970-B00A37CC8A76}"/>
   </bookViews>
@@ -128,7 +128,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
@@ -258,7 +259,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -281,23 +282,15 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -320,26 +313,28 @@
     <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="2" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="5" fillId="7" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="5" fillId="7" borderId="1" xfId="4" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="20% - Ênfase2" xfId="2" builtinId="34"/>
     <cellStyle name="60% - Ênfase2" xfId="3" builtinId="36"/>
     <cellStyle name="Ênfase5" xfId="1" builtinId="45"/>
+    <cellStyle name="Moeda" xfId="4" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="13">
@@ -1971,15 +1966,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
       <c r="H1" s="7">
         <f ca="1">TODAY()</f>
         <v>46286</v>
@@ -2226,7 +2221,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7194E76-DEDA-4B2E-94B4-90155E6067DA}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
@@ -2238,152 +2233,155 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="10">
         <v>12000</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="10">
         <v>7000</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="11">
         <v>0.1</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="16">
         <f>IF(C4&lt;D4,0,C4*E4)</f>
         <v>1200</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="10">
         <v>14000</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <v>8000</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="11">
         <v>0.1</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="16">
         <f t="shared" ref="F5:F7" si="0">IF(C5&lt;D5,0,C5*E5)</f>
         <v>1400</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="10">
         <v>8000</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="10">
         <v>5000</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="11">
         <v>0.1</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="16">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="10">
         <v>9000</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="10">
         <v>7000</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="11">
         <v>0.1</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="16">
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="15"/>
+      <c r="B10" s="17"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="14">
+      <c r="A11" s="12">
         <v>1</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="12">
         <f>LARGE(F4:F7,1)</f>
         <v>1400</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="14">
+      <c r="A12" s="12">
         <v>2</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="12">
         <f>LARGE(F4:F7,2)</f>
         <v>1200</v>
       </c>
-      <c r="C12" s="16"/>
+      <c r="C12" s="13"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="14">
+      <c r="A13" s="12">
         <v>3</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="12">
         <f>LARGE(F4:F7,3)</f>
         <v>900</v>
       </c>
+    </row>
+    <row r="23" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D23" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/AULA 02-PTIC.xlsx
+++ b/AULA 02-PTIC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CAMARGO\Desktop\PTIC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1418F2E-291D-4462-96C0-17705FFB1462}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387D9E8E-7BFC-41B7-83F4-1C32A9DCB44D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{28501F88-7677-4DF6-9970-B00A37CC8A76}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>Planilha de notas</t>
   </si>
@@ -122,6 +122,12 @@
   </si>
   <si>
     <t>Valor de Comissão alta</t>
+  </si>
+  <si>
+    <t>Salário</t>
+  </si>
+  <si>
+    <t>Valor recebido</t>
   </si>
 </sst>
 </file>
@@ -192,7 +198,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -258,6 +264,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -290,7 +302,7 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -313,21 +325,41 @@
     <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="2" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="5" fillId="7" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="7" borderId="1" xfId="4" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="7" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="7" borderId="1" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="12" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1966,15 +1998,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
       <c r="H1" s="7">
         <f ca="1">TODAY()</f>
         <v>46286</v>
@@ -2221,167 +2253,192 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7194E76-DEDA-4B2E-94B4-90155E6067DA}">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="9" t="s">
         <v>25</v>
       </c>
+      <c r="G3" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="13">
         <v>12000</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="13">
         <v>7000</v>
       </c>
-      <c r="E4" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="F4" s="16">
+      <c r="E4" s="14">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F4" s="15">
         <f>IF(C4&lt;D4,0,C4*E4)</f>
-        <v>1200</v>
-      </c>
+        <v>840.00000000000011</v>
+      </c>
+      <c r="G4" s="16">
+        <v>1850</v>
+      </c>
+      <c r="H4" s="17"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="13">
         <v>14000</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="13">
         <v>8000</v>
       </c>
-      <c r="E5" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="F5" s="16">
+      <c r="E5" s="14">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F5" s="15">
         <f t="shared" ref="F5:F7" si="0">IF(C5&lt;D5,0,C5*E5)</f>
-        <v>1400</v>
-      </c>
+        <v>980.00000000000011</v>
+      </c>
+      <c r="G5" s="16">
+        <v>1850</v>
+      </c>
+      <c r="H5" s="17"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="13">
         <v>8000</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="13">
         <v>5000</v>
       </c>
-      <c r="E6" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="F6" s="16">
+      <c r="E6" s="14">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F6" s="15">
         <f t="shared" si="0"/>
-        <v>800</v>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="G6" s="16">
+        <v>1850</v>
+      </c>
+      <c r="H6" s="17"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="13">
         <v>9000</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="13">
         <v>7000</v>
       </c>
-      <c r="E7" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="F7" s="16">
+      <c r="E7" s="14">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F7" s="15">
         <f t="shared" si="0"/>
-        <v>900</v>
-      </c>
+        <v>630.00000000000011</v>
+      </c>
+      <c r="G7" s="16">
+        <v>1850</v>
+      </c>
+      <c r="H7" s="17"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="17"/>
+      <c r="B10" s="11"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="18">
         <v>1</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="18">
         <f>LARGE(F4:F7,1)</f>
-        <v>1400</v>
+        <v>980.00000000000011</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="12">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="18">
         <v>2</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="18">
         <f>LARGE(F4:F7,2)</f>
-        <v>1200</v>
-      </c>
-      <c r="C12" s="13"/>
+        <v>840.00000000000011</v>
+      </c>
+      <c r="C12" s="19"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="12">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="18">
         <v>3</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="18">
         <f>LARGE(F4:F7,3)</f>
-        <v>900</v>
+        <v>630.00000000000011</v>
       </c>
     </row>
     <row r="23" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D23" s="13"/>
+      <c r="D23" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="2">
